--- a/events/Racice_2013_WC/Racice_2013_WC_Results.xlsx
+++ b/events/Racice_2013_WC/Racice_2013_WC_Results.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X1228"/>
+  <dimension ref="A1:X1293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11596,11 +11596,6 @@
           <t>4:16.191</t>
         </is>
       </c>
-      <c r="R173" t="inlineStr">
-        <is>
-          <t>47779</t>
-        </is>
-      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -44993,11 +44988,6 @@
           <t>4:04.496</t>
         </is>
       </c>
-      <c r="R681" t="inlineStr">
-        <is>
-          <t>47779</t>
-        </is>
-      </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
@@ -80886,6 +80876,3686 @@
       <c r="X1228" t="inlineStr">
         <is>
           <t>DSQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D1229" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1229" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1229" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1229" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1229" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="K1229" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="M1229" t="n">
+        <v>1</v>
+      </c>
+      <c r="N1229" t="n">
+        <v>1</v>
+      </c>
+      <c r="P1229" t="inlineStr">
+        <is>
+          <t>23:00.1</t>
+        </is>
+      </c>
+      <c r="R1229" t="inlineStr">
+        <is>
+          <t>42447</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D1230" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1230" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1230" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1230" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1230" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="K1230" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="M1230" t="n">
+        <v>2</v>
+      </c>
+      <c r="N1230" t="n">
+        <v>2</v>
+      </c>
+      <c r="P1230" t="inlineStr">
+        <is>
+          <t>23:03.4</t>
+        </is>
+      </c>
+      <c r="R1230" t="inlineStr">
+        <is>
+          <t>36587</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1231" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D1231" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1231" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1231" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1231" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1231" t="inlineStr">
+        <is>
+          <t>SVK</t>
+        </is>
+      </c>
+      <c r="K1231" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="M1231" t="n">
+        <v>3</v>
+      </c>
+      <c r="N1231" t="n">
+        <v>3</v>
+      </c>
+      <c r="P1231" t="inlineStr">
+        <is>
+          <t>23:11.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D1232" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1232" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1232" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1232" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1232" t="inlineStr">
+        <is>
+          <t>SVK</t>
+        </is>
+      </c>
+      <c r="K1232" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="M1232" t="n">
+        <v>4</v>
+      </c>
+      <c r="N1232" t="n">
+        <v>4</v>
+      </c>
+      <c r="P1232" t="inlineStr">
+        <is>
+          <t>23:11.7</t>
+        </is>
+      </c>
+      <c r="R1232" t="inlineStr">
+        <is>
+          <t>44427</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1233" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D1233" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1233" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1233" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1233" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1233" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="K1233" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="M1233" t="n">
+        <v>5</v>
+      </c>
+      <c r="N1233" t="n">
+        <v>5</v>
+      </c>
+      <c r="P1233" t="inlineStr">
+        <is>
+          <t>23:27.2</t>
+        </is>
+      </c>
+      <c r="R1233" t="inlineStr">
+        <is>
+          <t>42471</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1234" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D1234" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1234" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1234" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1234" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1234" t="inlineStr">
+        <is>
+          <t>UZB</t>
+        </is>
+      </c>
+      <c r="K1234" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="M1234" t="n">
+        <v>6</v>
+      </c>
+      <c r="N1234" t="n">
+        <v>6</v>
+      </c>
+      <c r="P1234" t="inlineStr">
+        <is>
+          <t>24:10.1</t>
+        </is>
+      </c>
+      <c r="R1234" t="inlineStr">
+        <is>
+          <t>47674</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D1235" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1235" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1235" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1235" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1235" t="inlineStr">
+        <is>
+          <t>CZE</t>
+        </is>
+      </c>
+      <c r="K1235" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="M1235" t="n">
+        <v>7</v>
+      </c>
+      <c r="N1235" t="n">
+        <v>7</v>
+      </c>
+      <c r="P1235" t="inlineStr">
+        <is>
+          <t>24:20.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1236" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D1236" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1236" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1236" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1236" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1236" t="inlineStr">
+        <is>
+          <t>KAZ</t>
+        </is>
+      </c>
+      <c r="K1236" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="M1236" t="n">
+        <v>8</v>
+      </c>
+      <c r="N1236" t="n">
+        <v>8</v>
+      </c>
+      <c r="P1236" t="inlineStr">
+        <is>
+          <t>24:25.3</t>
+        </is>
+      </c>
+      <c r="R1236" t="inlineStr">
+        <is>
+          <t>42569</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1237" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D1237" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1237" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1237" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1237" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1237" t="inlineStr">
+        <is>
+          <t>CZE</t>
+        </is>
+      </c>
+      <c r="K1237" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="M1237" t="n">
+        <v>9</v>
+      </c>
+      <c r="N1237" t="n">
+        <v>9</v>
+      </c>
+      <c r="P1237" t="inlineStr">
+        <is>
+          <t>24:34.0</t>
+        </is>
+      </c>
+      <c r="R1237" t="inlineStr">
+        <is>
+          <t>42364</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1238" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D1238" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1238" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1238" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1238" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1238" t="inlineStr">
+        <is>
+          <t>POL</t>
+        </is>
+      </c>
+      <c r="K1238" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="M1238" t="n">
+        <v>10</v>
+      </c>
+      <c r="N1238" t="n">
+        <v>10</v>
+      </c>
+      <c r="P1238" t="inlineStr">
+        <is>
+          <t>24:36.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1239" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D1239" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1239" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1239" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1239" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1239" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="K1239" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="M1239" t="n">
+        <v>11</v>
+      </c>
+      <c r="N1239" t="n">
+        <v>11</v>
+      </c>
+      <c r="P1239" t="inlineStr">
+        <is>
+          <t>24:41.1</t>
+        </is>
+      </c>
+      <c r="R1239" t="inlineStr">
+        <is>
+          <t>36565</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1240" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D1240" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1240" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1240" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1240" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1240" t="inlineStr">
+        <is>
+          <t>RUS</t>
+        </is>
+      </c>
+      <c r="K1240" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="M1240" t="n">
+        <v>12</v>
+      </c>
+      <c r="N1240" t="n">
+        <v>12</v>
+      </c>
+      <c r="P1240" t="inlineStr">
+        <is>
+          <t>25:05.8</t>
+        </is>
+      </c>
+      <c r="R1240" t="inlineStr">
+        <is>
+          <t>36163</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1241" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D1241" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1241" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1241" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1241" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1241" t="inlineStr">
+        <is>
+          <t>KAZ</t>
+        </is>
+      </c>
+      <c r="K1241" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="R1241" t="inlineStr">
+        <is>
+          <t>42562</t>
+        </is>
+      </c>
+      <c r="X1241" t="inlineStr">
+        <is>
+          <t>DNF</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1242" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D1242" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1242" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1242" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1242" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1242" t="inlineStr">
+        <is>
+          <t>UZB</t>
+        </is>
+      </c>
+      <c r="K1242" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="X1242" t="inlineStr">
+        <is>
+          <t>DNF</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1243" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1243" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1243" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1243" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1243" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1243" t="inlineStr">
+        <is>
+          <t>AUS</t>
+        </is>
+      </c>
+      <c r="K1243" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="M1243" t="n">
+        <v>1</v>
+      </c>
+      <c r="N1243" t="n">
+        <v>1</v>
+      </c>
+      <c r="P1243" t="inlineStr">
+        <is>
+          <t>22:16.9</t>
+        </is>
+      </c>
+      <c r="R1243" t="inlineStr">
+        <is>
+          <t>42209</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1244" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1244" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1244" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1244" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1244" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1244" t="inlineStr">
+        <is>
+          <t>AUS</t>
+        </is>
+      </c>
+      <c r="K1244" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="M1244" t="n">
+        <v>2</v>
+      </c>
+      <c r="N1244" t="n">
+        <v>2</v>
+      </c>
+      <c r="P1244" t="inlineStr">
+        <is>
+          <t>22:18.6</t>
+        </is>
+      </c>
+      <c r="R1244" t="inlineStr">
+        <is>
+          <t>42173</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1245" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1245" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1245" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1245" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1245" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1245" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="K1245" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="M1245" t="n">
+        <v>3</v>
+      </c>
+      <c r="N1245" t="n">
+        <v>3</v>
+      </c>
+      <c r="P1245" t="inlineStr">
+        <is>
+          <t>22:19.4</t>
+        </is>
+      </c>
+      <c r="R1245" t="inlineStr">
+        <is>
+          <t>48772</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1246" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1246" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1246" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1246" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1246" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1246" t="inlineStr">
+        <is>
+          <t>NZL</t>
+        </is>
+      </c>
+      <c r="K1246" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="M1246" t="n">
+        <v>4</v>
+      </c>
+      <c r="N1246" t="n">
+        <v>4</v>
+      </c>
+      <c r="P1246" t="inlineStr">
+        <is>
+          <t>22:36.2</t>
+        </is>
+      </c>
+      <c r="R1246" t="inlineStr">
+        <is>
+          <t>36283</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1247" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1247" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1247" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1247" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1247" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1247" t="inlineStr">
+        <is>
+          <t>CZE</t>
+        </is>
+      </c>
+      <c r="K1247" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="M1247" t="n">
+        <v>5</v>
+      </c>
+      <c r="N1247" t="n">
+        <v>5</v>
+      </c>
+      <c r="P1247" t="inlineStr">
+        <is>
+          <t>22:40.9</t>
+        </is>
+      </c>
+      <c r="R1247" t="inlineStr">
+        <is>
+          <t>35779</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1248" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1248" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1248" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1248" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1248" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1248" t="inlineStr">
+        <is>
+          <t>NOR</t>
+        </is>
+      </c>
+      <c r="K1248" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="M1248" t="n">
+        <v>6</v>
+      </c>
+      <c r="N1248" t="n">
+        <v>6</v>
+      </c>
+      <c r="P1248" t="inlineStr">
+        <is>
+          <t>22:41.9</t>
+        </is>
+      </c>
+      <c r="R1248" t="inlineStr">
+        <is>
+          <t>35984</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1249" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1249" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1249" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1249" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1249" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1249" t="inlineStr">
+        <is>
+          <t>CZE</t>
+        </is>
+      </c>
+      <c r="K1249" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="M1249" t="n">
+        <v>7</v>
+      </c>
+      <c r="N1249" t="n">
+        <v>7</v>
+      </c>
+      <c r="P1249" t="inlineStr">
+        <is>
+          <t>22:52.5</t>
+        </is>
+      </c>
+      <c r="R1249" t="inlineStr">
+        <is>
+          <t>35908</t>
+        </is>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1250" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1250" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1250" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1250" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1250" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1250" t="inlineStr">
+        <is>
+          <t>FIN</t>
+        </is>
+      </c>
+      <c r="K1250" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="M1250" t="n">
+        <v>8</v>
+      </c>
+      <c r="N1250" t="n">
+        <v>8</v>
+      </c>
+      <c r="P1250" t="inlineStr">
+        <is>
+          <t>22:59.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1251" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1251" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1251" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1251" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1251" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1251" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="K1251" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="M1251" t="n">
+        <v>9</v>
+      </c>
+      <c r="N1251" t="n">
+        <v>9</v>
+      </c>
+      <c r="P1251" t="inlineStr">
+        <is>
+          <t>23:01.8</t>
+        </is>
+      </c>
+      <c r="R1251" t="inlineStr">
+        <is>
+          <t>42360</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1252" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1252" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1252" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1252" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1252" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1252" t="inlineStr">
+        <is>
+          <t>AUT</t>
+        </is>
+      </c>
+      <c r="K1252" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="M1252" t="n">
+        <v>10</v>
+      </c>
+      <c r="N1252" t="n">
+        <v>10</v>
+      </c>
+      <c r="P1252" t="inlineStr">
+        <is>
+          <t>23:15.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1253" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1253" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1253" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1253" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1253" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1253" t="inlineStr">
+        <is>
+          <t>NED</t>
+        </is>
+      </c>
+      <c r="K1253" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="M1253" t="n">
+        <v>11</v>
+      </c>
+      <c r="N1253" t="n">
+        <v>11</v>
+      </c>
+      <c r="P1253" t="inlineStr">
+        <is>
+          <t>23:15.9</t>
+        </is>
+      </c>
+      <c r="R1253" t="inlineStr">
+        <is>
+          <t>35924</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1254" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1254" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1254" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1254" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1254" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1254" t="inlineStr">
+        <is>
+          <t>NOR</t>
+        </is>
+      </c>
+      <c r="K1254" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="M1254" t="n">
+        <v>12</v>
+      </c>
+      <c r="N1254" t="n">
+        <v>12</v>
+      </c>
+      <c r="P1254" t="inlineStr">
+        <is>
+          <t>23:30.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1255" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1255" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1255" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1255" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1255" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1255" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="K1255" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="M1255" t="n">
+        <v>13</v>
+      </c>
+      <c r="N1255" t="n">
+        <v>13</v>
+      </c>
+      <c r="P1255" t="inlineStr">
+        <is>
+          <t>23:39.4</t>
+        </is>
+      </c>
+      <c r="R1255" t="inlineStr">
+        <is>
+          <t>42483</t>
+        </is>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1256" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1256" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1256" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1256" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1256" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1256" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="K1256" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="M1256" t="n">
+        <v>14</v>
+      </c>
+      <c r="N1256" t="n">
+        <v>14</v>
+      </c>
+      <c r="P1256" t="inlineStr">
+        <is>
+          <t>23:51.4</t>
+        </is>
+      </c>
+      <c r="R1256" t="inlineStr">
+        <is>
+          <t>36579</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1257" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1257" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1257" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1257" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1257" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1257" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="K1257" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="M1257" t="n">
+        <v>15</v>
+      </c>
+      <c r="N1257" t="n">
+        <v>15</v>
+      </c>
+      <c r="P1257" t="inlineStr">
+        <is>
+          <t>23:54.7</t>
+        </is>
+      </c>
+      <c r="R1257" t="inlineStr">
+        <is>
+          <t>42485</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1258" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1258" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1258" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1258" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1258" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1258" t="inlineStr">
+        <is>
+          <t>RUS</t>
+        </is>
+      </c>
+      <c r="K1258" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="M1258" t="n">
+        <v>16</v>
+      </c>
+      <c r="N1258" t="n">
+        <v>16</v>
+      </c>
+      <c r="P1258" t="inlineStr">
+        <is>
+          <t>24:28.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1259" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1259" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1259" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1259" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1259" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1259" t="inlineStr">
+        <is>
+          <t>NED</t>
+        </is>
+      </c>
+      <c r="K1259" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="M1259" t="n">
+        <v>17</v>
+      </c>
+      <c r="N1259" t="n">
+        <v>17</v>
+      </c>
+      <c r="P1259" t="inlineStr">
+        <is>
+          <t>24:57.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1260" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1260" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1260" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1260" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1260" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1260" t="inlineStr">
+        <is>
+          <t>GBR</t>
+        </is>
+      </c>
+      <c r="K1260" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="R1260" t="inlineStr">
+        <is>
+          <t>35812</t>
+        </is>
+      </c>
+      <c r="X1260" t="inlineStr">
+        <is>
+          <t>DNS</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1261" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1261" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1261" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1261" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1261" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1261" t="inlineStr">
+        <is>
+          <t>BLR</t>
+        </is>
+      </c>
+      <c r="K1261" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="M1261" t="n">
+        <v>1</v>
+      </c>
+      <c r="N1261" t="n">
+        <v>1</v>
+      </c>
+      <c r="P1261" t="inlineStr">
+        <is>
+          <t>19:49.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1262" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1262" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1262" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1262" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1262" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1262" t="inlineStr">
+        <is>
+          <t>AUS</t>
+        </is>
+      </c>
+      <c r="K1262" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="M1262" t="n">
+        <v>2</v>
+      </c>
+      <c r="N1262" t="n">
+        <v>2</v>
+      </c>
+      <c r="P1262" t="inlineStr">
+        <is>
+          <t>19:50.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1263" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1263" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1263" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1263" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1263" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1263" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="K1263" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="M1263" t="n">
+        <v>3</v>
+      </c>
+      <c r="N1263" t="n">
+        <v>3</v>
+      </c>
+      <c r="P1263" t="inlineStr">
+        <is>
+          <t>19:52.9</t>
+        </is>
+      </c>
+      <c r="R1263" t="inlineStr">
+        <is>
+          <t>42336</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1264" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1264" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1264" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1264" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1264" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1264" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="K1264" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="M1264" t="n">
+        <v>4</v>
+      </c>
+      <c r="N1264" t="n">
+        <v>4</v>
+      </c>
+      <c r="P1264" t="inlineStr">
+        <is>
+          <t>19:53.7</t>
+        </is>
+      </c>
+      <c r="R1264" t="inlineStr">
+        <is>
+          <t>42341</t>
+        </is>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1265" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1265" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1265" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1265" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1265" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1265" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="K1265" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="M1265" t="n">
+        <v>5</v>
+      </c>
+      <c r="N1265" t="n">
+        <v>5</v>
+      </c>
+      <c r="P1265" t="inlineStr">
+        <is>
+          <t>20:10.4</t>
+        </is>
+      </c>
+      <c r="R1265" t="inlineStr">
+        <is>
+          <t>36567</t>
+        </is>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1266" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1266" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1266" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1266" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1266" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1266" t="inlineStr">
+        <is>
+          <t>SRB</t>
+        </is>
+      </c>
+      <c r="K1266" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="M1266" t="n">
+        <v>6</v>
+      </c>
+      <c r="N1266" t="n">
+        <v>6</v>
+      </c>
+      <c r="P1266" t="inlineStr">
+        <is>
+          <t>20:31.8</t>
+        </is>
+      </c>
+      <c r="R1266" t="inlineStr">
+        <is>
+          <t>42184</t>
+        </is>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1267" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1267" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1267" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1267" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1267" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1267" t="inlineStr">
+        <is>
+          <t>SLO</t>
+        </is>
+      </c>
+      <c r="K1267" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="M1267" t="n">
+        <v>7</v>
+      </c>
+      <c r="N1267" t="n">
+        <v>7</v>
+      </c>
+      <c r="P1267" t="inlineStr">
+        <is>
+          <t>20:37.5</t>
+        </is>
+      </c>
+      <c r="R1267" t="inlineStr">
+        <is>
+          <t>36310</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1268" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1268" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1268" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1268" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1268" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1268" t="inlineStr">
+        <is>
+          <t>CZE</t>
+        </is>
+      </c>
+      <c r="K1268" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="M1268" t="n">
+        <v>8</v>
+      </c>
+      <c r="N1268" t="n">
+        <v>8</v>
+      </c>
+      <c r="P1268" t="inlineStr">
+        <is>
+          <t>20:40.7</t>
+        </is>
+      </c>
+      <c r="R1268" t="inlineStr">
+        <is>
+          <t>35776</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1269" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1269" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1269" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1269" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1269" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1269" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="K1269" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="M1269" t="n">
+        <v>9</v>
+      </c>
+      <c r="N1269" t="n">
+        <v>9</v>
+      </c>
+      <c r="P1269" t="inlineStr">
+        <is>
+          <t>20:42.6</t>
+        </is>
+      </c>
+      <c r="R1269" t="inlineStr">
+        <is>
+          <t>42285</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1270" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1270" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1270" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1270" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1270" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1270" t="inlineStr">
+        <is>
+          <t>GBR</t>
+        </is>
+      </c>
+      <c r="K1270" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="M1270" t="n">
+        <v>10</v>
+      </c>
+      <c r="N1270" t="n">
+        <v>10</v>
+      </c>
+      <c r="P1270" t="inlineStr">
+        <is>
+          <t>20:43.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1271" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1271" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1271" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1271" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1271" t="inlineStr">
+        <is>
+          <t>NOR</t>
+        </is>
+      </c>
+      <c r="K1271" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="M1271" t="n">
+        <v>11</v>
+      </c>
+      <c r="N1271" t="n">
+        <v>11</v>
+      </c>
+      <c r="P1271" t="inlineStr">
+        <is>
+          <t>20:44.5</t>
+        </is>
+      </c>
+      <c r="R1271" t="inlineStr">
+        <is>
+          <t>35981</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1272" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1272" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1272" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1272" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1272" t="inlineStr">
+        <is>
+          <t>CZE</t>
+        </is>
+      </c>
+      <c r="K1272" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="M1272" t="n">
+        <v>12</v>
+      </c>
+      <c r="N1272" t="n">
+        <v>12</v>
+      </c>
+      <c r="P1272" t="inlineStr">
+        <is>
+          <t>20:48.2</t>
+        </is>
+      </c>
+      <c r="R1272" t="inlineStr">
+        <is>
+          <t>35782</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1273" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1273" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1273" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1273" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1273" t="inlineStr">
+        <is>
+          <t>NZL</t>
+        </is>
+      </c>
+      <c r="K1273" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="M1273" t="n">
+        <v>13</v>
+      </c>
+      <c r="N1273" t="n">
+        <v>13</v>
+      </c>
+      <c r="P1273" t="inlineStr">
+        <is>
+          <t>20:49.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1274" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1274" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1274" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1274" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1274" t="inlineStr">
+        <is>
+          <t>SUI</t>
+        </is>
+      </c>
+      <c r="K1274" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="M1274" t="n">
+        <v>14</v>
+      </c>
+      <c r="N1274" t="n">
+        <v>14</v>
+      </c>
+      <c r="P1274" t="inlineStr">
+        <is>
+          <t>20:51.7</t>
+        </is>
+      </c>
+      <c r="R1274" t="inlineStr">
+        <is>
+          <t>42232</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1275" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1275" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1275" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1275" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1275" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="K1275" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="M1275" t="n">
+        <v>15</v>
+      </c>
+      <c r="N1275" t="n">
+        <v>15</v>
+      </c>
+      <c r="P1275" t="inlineStr">
+        <is>
+          <t>21:13.6</t>
+        </is>
+      </c>
+      <c r="R1275" t="inlineStr">
+        <is>
+          <t>42422</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1276" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1276" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1276" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1276" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1276" t="inlineStr">
+        <is>
+          <t>UZB</t>
+        </is>
+      </c>
+      <c r="K1276" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="M1276" t="n">
+        <v>16</v>
+      </c>
+      <c r="N1276" t="n">
+        <v>16</v>
+      </c>
+      <c r="P1276" t="inlineStr">
+        <is>
+          <t>21:19.6</t>
+        </is>
+      </c>
+      <c r="R1276" t="inlineStr">
+        <is>
+          <t>52232</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1277" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1277" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1277" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1277" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1277" t="inlineStr">
+        <is>
+          <t>KAZ</t>
+        </is>
+      </c>
+      <c r="K1277" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="M1277" t="n">
+        <v>17</v>
+      </c>
+      <c r="N1277" t="n">
+        <v>17</v>
+      </c>
+      <c r="P1277" t="inlineStr">
+        <is>
+          <t>21:26.7</t>
+        </is>
+      </c>
+      <c r="R1277" t="inlineStr">
+        <is>
+          <t>42567</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1278" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1278" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1278" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1278" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1278" t="inlineStr">
+        <is>
+          <t>SRB</t>
+        </is>
+      </c>
+      <c r="K1278" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="M1278" t="n">
+        <v>18</v>
+      </c>
+      <c r="N1278" t="n">
+        <v>18</v>
+      </c>
+      <c r="P1278" t="inlineStr">
+        <is>
+          <t>21:35.4</t>
+        </is>
+      </c>
+      <c r="R1278" t="inlineStr">
+        <is>
+          <t>42179</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1279" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1279" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1279" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1279" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1279" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1279" t="inlineStr">
+        <is>
+          <t>BLR</t>
+        </is>
+      </c>
+      <c r="K1279" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="M1279" t="n">
+        <v>19</v>
+      </c>
+      <c r="N1279" t="n">
+        <v>19</v>
+      </c>
+      <c r="P1279" t="inlineStr">
+        <is>
+          <t>21:36.1</t>
+        </is>
+      </c>
+      <c r="R1279" t="inlineStr">
+        <is>
+          <t>42063</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1280" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1280" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1280" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1280" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1280" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1280" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="K1280" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="M1280" t="n">
+        <v>20</v>
+      </c>
+      <c r="N1280" t="n">
+        <v>20</v>
+      </c>
+      <c r="P1280" t="inlineStr">
+        <is>
+          <t>21:45.1</t>
+        </is>
+      </c>
+      <c r="R1280" t="inlineStr">
+        <is>
+          <t>41787</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1281" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1281" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1281" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1281" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1281" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1281" t="inlineStr">
+        <is>
+          <t>SVK</t>
+        </is>
+      </c>
+      <c r="K1281" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="M1281" t="n">
+        <v>21</v>
+      </c>
+      <c r="N1281" t="n">
+        <v>21</v>
+      </c>
+      <c r="P1281" t="inlineStr">
+        <is>
+          <t>21:47.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1282" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1282" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1282" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1282" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1282" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1282" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="K1282" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="M1282" t="n">
+        <v>22</v>
+      </c>
+      <c r="N1282" t="n">
+        <v>22</v>
+      </c>
+      <c r="P1282" t="inlineStr">
+        <is>
+          <t>21:51.4</t>
+        </is>
+      </c>
+      <c r="R1282" t="inlineStr">
+        <is>
+          <t>42488</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1283" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1283" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1283" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1283" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1283" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1283" t="inlineStr">
+        <is>
+          <t>FIN</t>
+        </is>
+      </c>
+      <c r="K1283" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="M1283" t="n">
+        <v>23</v>
+      </c>
+      <c r="N1283" t="n">
+        <v>23</v>
+      </c>
+      <c r="P1283" t="inlineStr">
+        <is>
+          <t>21:54.0</t>
+        </is>
+      </c>
+      <c r="R1283" t="inlineStr">
+        <is>
+          <t>36604</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1284" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1284" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1284" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1284" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1284" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1284" t="inlineStr">
+        <is>
+          <t>AUT</t>
+        </is>
+      </c>
+      <c r="K1284" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="M1284" t="n">
+        <v>24</v>
+      </c>
+      <c r="N1284" t="n">
+        <v>24</v>
+      </c>
+      <c r="P1284" t="inlineStr">
+        <is>
+          <t>21:54.8</t>
+        </is>
+      </c>
+      <c r="R1284" t="inlineStr">
+        <is>
+          <t>35567</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1285" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1285" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1285" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1285" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1285" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1285" t="inlineStr">
+        <is>
+          <t>AZE</t>
+        </is>
+      </c>
+      <c r="K1285" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="M1285" t="n">
+        <v>25</v>
+      </c>
+      <c r="N1285" t="n">
+        <v>25</v>
+      </c>
+      <c r="P1285" t="inlineStr">
+        <is>
+          <t>22:44.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1286" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1286" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1286" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1286" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1286" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1286" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="K1286" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="M1286" t="n">
+        <v>26</v>
+      </c>
+      <c r="N1286" t="n">
+        <v>26</v>
+      </c>
+      <c r="P1286" t="inlineStr">
+        <is>
+          <t>22:49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1287" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1287" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1287" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1287" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1287" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1287" t="inlineStr">
+        <is>
+          <t>RUS</t>
+        </is>
+      </c>
+      <c r="K1287" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="X1287" t="inlineStr">
+        <is>
+          <t>DNS</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1288" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1288" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1288" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1288" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1288" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1288" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="K1288" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="R1288" t="inlineStr">
+        <is>
+          <t>42587</t>
+        </is>
+      </c>
+      <c r="X1288" t="inlineStr">
+        <is>
+          <t>DNF</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1289" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1289" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1289" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1289" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1289" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1289" t="inlineStr">
+        <is>
+          <t>NOR</t>
+        </is>
+      </c>
+      <c r="K1289" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="R1289" t="inlineStr">
+        <is>
+          <t>36742</t>
+        </is>
+      </c>
+      <c r="X1289" t="inlineStr">
+        <is>
+          <t>DNF</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1290" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1290" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1290" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1290" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1290" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1290" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="K1290" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="R1290" t="inlineStr">
+        <is>
+          <t>41784</t>
+        </is>
+      </c>
+      <c r="X1290" t="inlineStr">
+        <is>
+          <t>DNF</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1291" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1291" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1291" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1291" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1291" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1291" t="inlineStr">
+        <is>
+          <t>KAZ</t>
+        </is>
+      </c>
+      <c r="K1291" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="R1291" t="inlineStr">
+        <is>
+          <t>42558</t>
+        </is>
+      </c>
+      <c r="X1291" t="inlineStr">
+        <is>
+          <t>DNF</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1292" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1292" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1292" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1292" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1292" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1292" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1292" t="inlineStr">
+        <is>
+          <t>UZB</t>
+        </is>
+      </c>
+      <c r="K1292" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="X1292" t="inlineStr">
+        <is>
+          <t>DNF</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1293" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1293" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1293" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1293" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1293" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1293" s="2" t="n">
+        <v>41413</v>
+      </c>
+      <c r="I1293" t="inlineStr">
+        <is>
+          <t>AZE</t>
+        </is>
+      </c>
+      <c r="K1293" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="X1293" t="inlineStr">
+        <is>
+          <t>DNF</t>
         </is>
       </c>
     </row>
@@ -81170,17 +84840,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>47779</t>
+          <t>35812</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Krisztina</t>
+          <t>Lani</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BEDOCS</t>
+          <t>BELCHER</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -81192,17 +84862,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>35812</t>
+          <t>42550</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lani</t>
+          <t>Abir</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BELCHER</t>
+          <t>BEN ISMAIL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -81214,12 +84884,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>42550</t>
+          <t>42549</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Abir</t>
+          <t>Afef</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -81236,39 +84906,39 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>42549</t>
+          <t>36567</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Afef</t>
+          <t>Maximilian</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BEN ISMAIL</t>
+          <t>BENASSI</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>36567</t>
+          <t>44433</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Maximilian</t>
+          <t>Lubomir</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BENASSI</t>
+          <t>BENO</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -81280,17 +84950,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>44433</t>
+          <t>42558</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lubomir</t>
+          <t>Yuriy</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BENO</t>
+          <t>BEREZINTSEV</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -81302,17 +84972,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>42558</t>
+          <t>35291</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Yuriy</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BEREZINTSEV</t>
+          <t>BEUGNET</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -81324,17 +84994,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>35291</t>
+          <t>42049</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Vitaliy</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BEUGNET</t>
+          <t>BIALKO</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -81346,17 +85016,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>42049</t>
+          <t>42183</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vitaliy</t>
+          <t>Simo</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BIALKO</t>
+          <t>BOLTIC</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -81368,17 +85038,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>42183</t>
+          <t>42454</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Simo</t>
+          <t>Maksim</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BOLTIC</t>
+          <t>BONDAR</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -81390,17 +85060,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>42454</t>
+          <t>52232</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Maksim</t>
+          <t>Sergey</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BONDAR</t>
+          <t>BORZOV</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -81412,17 +85082,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>52232</t>
+          <t>36162</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sergey</t>
+          <t>Alexey</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BORZOV</t>
+          <t>BOVDURETS</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -81434,17 +85104,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>36162</t>
+          <t>41592</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Alexey</t>
+          <t>Mathew</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BOVDURETS</t>
+          <t>BOWLEY</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -81456,17 +85126,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>41592</t>
+          <t>36232</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mathew</t>
+          <t>Jonathan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BOWLEY</t>
+          <t>BOYTON</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -81478,17 +85148,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>36232</t>
+          <t>35698</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Jonathan</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BOYTON</t>
+          <t>BRENDEL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -81500,34 +85170,34 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>35698</t>
+          <t>48772</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Lize</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BRENDEL</t>
+          <t>BROEKX</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>48772</t>
+          <t>41789</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Lize</t>
+          <t>Piet</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -81537,19 +85207,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>41789</t>
+          <t>48584</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Piet</t>
+          <t>Toon</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -81566,61 +85236,61 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>48584</t>
+          <t>35984</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Toon</t>
+          <t>Agnes</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BROEKX</t>
+          <t>BRUN-LIE</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>35984</t>
+          <t>42447</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Agnes</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BRUN-LIE</t>
+          <t>BRYANT</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>42447</t>
+          <t>35296</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Guillaume</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BRYANT</t>
+          <t>BURGER</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -81632,39 +85302,39 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>35296</t>
+          <t>36579</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Guillaume</t>
+          <t>Irene</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>BURGER</t>
+          <t>BURGO</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>36579</t>
+          <t>36580</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Irene</t>
+          <t>Sofia</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>BURGO</t>
+          <t>CAMPANA</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -81676,17 +85346,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>36580</t>
+          <t>36589</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Sofia</t>
+          <t>Francesca</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CAMPANA</t>
+          <t>CAPODIMONTE</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -81698,61 +85368,61 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>36589</t>
+          <t>35299</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Francesca</t>
+          <t>Cyrille</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CAPODIMONTE</t>
+          <t>CARRE</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>35299</t>
+          <t>36282</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cyrille</t>
+          <t>Lisa</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CARRE</t>
+          <t>CARRINGTON</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>36282</t>
+          <t>42884</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Lisa</t>
+          <t>Sara-Jane</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CARRINGTON</t>
+          <t>CAUMARTIN</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -81764,17 +85434,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>42884</t>
+          <t>35813</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Sara-Jane</t>
+          <t>Rachel</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CAUMARTIN</t>
+          <t>CAWTHORN</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -81786,39 +85456,39 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>35813</t>
+          <t>42428</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Rachel</t>
+          <t>Riccardo</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CAWTHORN</t>
+          <t>CECCHINI</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>42428</t>
+          <t>36153</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Riccardo</t>
+          <t>Nikolay</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CECCHINI</t>
+          <t>CHERVOV</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -81830,17 +85500,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>36153</t>
+          <t>42587</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nikolay</t>
+          <t>Tsz Chun</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CHERVOV</t>
+          <t>CHEUNG</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -81852,17 +85522,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>42587</t>
+          <t>36578</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tsz Chun</t>
+          <t>Edoardo</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CHEUNG</t>
+          <t>CHIERINI</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -81874,17 +85544,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>36578</t>
+          <t>42449</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Edoardo</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CHIERINI</t>
+          <t>COCHRANE</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -81896,17 +85566,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>42449</t>
+          <t>42419</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Nicolae</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>COCHRANE</t>
+          <t>CRACIUN</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -81918,12 +85588,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>42419</t>
+          <t>36587</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nicolae</t>
+          <t>Sergiu</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -81940,17 +85610,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>36587</t>
+          <t>36584</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Sergiu</t>
+          <t>Mauro</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CRACIUN</t>
+          <t>CRENNA</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -81962,17 +85632,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>36584</t>
+          <t>36231</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Mauro</t>
+          <t>Andrew</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CRENNA</t>
+          <t>DANIELS</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -81984,17 +85654,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>36231</t>
+          <t>35782</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Andrew</t>
+          <t>Pavel</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DANIELS</t>
+          <t>DAVIDEK</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -82006,17 +85676,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>35782</t>
+          <t>42262</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Pavel</t>
+          <t>Cesar</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>DAVIDEK</t>
+          <t>DE CESARE</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -82028,17 +85698,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>42262</t>
+          <t>42450</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cesar</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DE CESARE</t>
+          <t>DE JONGE</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -82050,17 +85720,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>42450</t>
+          <t>41791</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Jonathan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DE JONGE</t>
+          <t>DELOMBAERDE</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -82072,17 +85742,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>41791</t>
+          <t>44424</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Jonathan</t>
+          <t>Viktor</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>DELOMBAERDE</t>
+          <t>DEMIN</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -82094,17 +85764,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>44424</t>
+          <t>42571</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Viktor</t>
+          <t>Alexey</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>DEMIN</t>
+          <t>DERGUNOV</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -82116,17 +85786,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>42571</t>
+          <t>36604</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Alexey</t>
+          <t>Miika</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>DERGUNOV</t>
+          <t>DIETRICH</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -82138,61 +85808,61 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>36604</t>
+          <t>35700</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Miika</t>
+          <t>Tina</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>DIETRICH</t>
+          <t>DIETZE</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>35700</t>
+          <t>42477</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tina</t>
+          <t>Igor</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>DIETZE</t>
+          <t>DOROFEEV</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>42477</t>
+          <t>35777</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Igor</t>
+          <t>Josef</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>DOROFEEV</t>
+          <t>DOSTAL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -82204,17 +85874,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>35777</t>
+          <t>42182</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Josef</t>
+          <t>Marko</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>DOSTAL</t>
+          <t>DRAGOSAVLJEVIC</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -82226,17 +85896,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>42182</t>
+          <t>42422</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Marko</t>
+          <t>Giulio</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>DRAGOSAVLJEVIC</t>
+          <t>DRESSINO</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -82248,61 +85918,61 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>42422</t>
+          <t>47112</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Giulio</t>
+          <t>Cathrin</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>DRESSINO</t>
+          <t>DUERR</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>47112</t>
+          <t>35548</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cathrin</t>
+          <t>Filip</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>DUERR</t>
+          <t>DVORAK</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>35548</t>
+          <t>36143</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Filip</t>
+          <t>Alexander</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>DVORAK</t>
+          <t>DYACHENKO</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -82314,17 +85984,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>36143</t>
+          <t>36205</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Alexander</t>
+          <t>Dmitrii</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>DYACHENKO</t>
+          <t>EKIMOV</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -82336,39 +86006,39 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>36205</t>
+          <t>42259</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Dmitrii</t>
+          <t>Lissette</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>EKIMOV</t>
+          <t>ESPINOZA</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>42259</t>
+          <t>42425</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Lissette</t>
+          <t>Agata</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t>FANTINI</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -82380,17 +86050,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>42425</t>
+          <t>35900</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Agata</t>
+          <t>Michaela</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>FANTINI</t>
+          <t>FASNEROVA</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -82402,39 +86072,39 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>35900</t>
+          <t>42407</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Michaela</t>
+          <t>Vladimir</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>FASNEROVA</t>
+          <t>FEDOSENKO</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>42407</t>
+          <t>36450</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Vladimir</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>FEDOSENKO</t>
+          <t>FERNANDES</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -82446,17 +86116,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>36450</t>
+          <t>36280</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Darryl</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>FERNANDES</t>
+          <t>FITZGERALD</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -82468,39 +86138,39 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>36280</t>
+          <t>42173</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Darryl</t>
+          <t>Naomi</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>FITZGERALD</t>
+          <t>FLOOD</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>42173</t>
+          <t>42453</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Naomi</t>
+          <t>Emilie</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>FLOOD</t>
+          <t>FOURNEL</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -82512,12 +86182,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>42453</t>
+          <t>42455</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Emilie</t>
+          <t>Hughes</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -82527,24 +86197,24 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>42455</t>
+          <t>35554</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Hughes</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>FOURNEL</t>
+          <t>FUKSA</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -82556,17 +86226,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>35554</t>
+          <t>44434</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>FUKSA</t>
+          <t>GELLE</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -82578,17 +86248,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>44434</t>
+          <t>56336</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Vyacheslav</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>GELLE</t>
+          <t>GORN</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -82600,17 +86270,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>56336</t>
+          <t>35318</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Vyacheslav</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>GORN</t>
+          <t>GOUBEL</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -82622,17 +86292,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>35318</t>
+          <t>35705</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Marcus</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>GOUBEL</t>
+          <t>GROSS</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -82644,17 +86314,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>35705</t>
+          <t>42304</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Marcus</t>
+          <t>Nebojsa</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>GROSS</t>
+          <t>GRUJIC</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -82666,39 +86336,39 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>42304</t>
+          <t>35321</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Nebojsa</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>GRUJIC</t>
+          <t>GUYOT</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>35321</t>
+          <t>35924</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Eef</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>GUYOT</t>
+          <t>HAAZE</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -82710,61 +86380,61 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>35924</t>
+          <t>41774</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Eef</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>HAAZE</t>
+          <t>HAKALA</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>41774</t>
+          <t>36220</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Angela</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>HAKALA</t>
+          <t>HANNAH</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>36220</t>
+          <t>42337</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Angela</t>
+          <t>Henriette Engel</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>HANNAH</t>
+          <t>HANSEN</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -82776,17 +86446,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>42337</t>
+          <t>36670</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Henriette Engel</t>
+          <t>Verena</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>HANSEN</t>
+          <t>HANTL</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -82798,39 +86468,39 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>36670</t>
+          <t>42042</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Verena</t>
+          <t>Dzianis</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>HANTL</t>
+          <t>HARAZHA</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>42042</t>
+          <t>42514</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Dzianis</t>
+          <t>Gordan</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>HARAZHA</t>
+          <t>HARBRECHT</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -82842,105 +86512,105 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>42514</t>
+          <t>36283</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Gordan</t>
+          <t>Teneale</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>HARBRECHT</t>
+          <t>HATTON</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>36283</t>
+          <t>35555</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Teneale</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>HATTON</t>
+          <t>HAVEL</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>35555</t>
+          <t>35788</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Andrea</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>HAVEL</t>
+          <t>HAVLOVA</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>35788</t>
+          <t>36228</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Andrea</t>
+          <t>Liam</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>HAVLOVA</t>
+          <t>HEATH</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>36228</t>
+          <t>35706</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Liam</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>HEATH</t>
+          <t>HENNIG</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -82952,61 +86622,61 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>35706</t>
+          <t>42519</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>HENNIG</t>
+          <t>HERING-PRADLER</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>42519</t>
+          <t>35993</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Lars</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>HERING-PRADLER</t>
+          <t>HJEMDAL</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>35993</t>
+          <t>35707</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Lars</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>HJEMDAL</t>
+          <t>HOFF</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -83018,61 +86688,61 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>35707</t>
+          <t>42360</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Margaret</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>HOFF</t>
+          <t>HOGAN</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>42360</t>
+          <t>35708</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Margaret</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>HOGAN</t>
+          <t>HOLLSTEIN</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>35708</t>
+          <t>42175</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Ervin</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>HOLLSTEIN</t>
+          <t>HOLPERT</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -83084,17 +86754,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>42175</t>
+          <t>35709</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Ervin</t>
+          <t>Stefan</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>HOLPERT</t>
+          <t>HOLTZ</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -83106,17 +86776,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>35709</t>
+          <t>42548</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Stefan</t>
+          <t>Khaled</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>HOLTZ</t>
+          <t>HOUCINE</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -83128,61 +86798,61 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>42548</t>
+          <t>35908</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Khaled</t>
+          <t>Lenka</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>HOUCINE</t>
+          <t>HROCHOVA</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>35908</t>
+          <t>35323</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Lenka</t>
+          <t>Etienne</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>HROCHOVA</t>
+          <t>HUBERT</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>35323</t>
+          <t>35324</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Etienne</t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>HUBERT</t>
+          <t>HYBOIS</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -83194,61 +86864,61 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>35324</t>
+          <t>42260</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Arnaud</t>
+          <t>Belen</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>HYBOIS</t>
+          <t>IBARRA</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>42260</t>
+          <t>69073</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Belen</t>
+          <t>Vilyam</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>IBARRA</t>
+          <t>IBRAGIMOV</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>69073</t>
+          <t>36565</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Vilyam</t>
+          <t>Luca</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>IBRAGIMOV</t>
+          <t>INCOLLINGO</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -83260,105 +86930,105 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>36565</t>
+          <t>42485</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Luca</t>
+          <t>Alexa</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>INCOLLINGO</t>
+          <t>IRVIN</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>42485</t>
+          <t>44425</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Alexa</t>
+          <t>Gabor</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>IRVIN</t>
+          <t>JAKUBIK</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>44425</t>
+          <t>35325</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Gabor</t>
+          <t>Lea</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>JAKUBIK</t>
+          <t>JAMELOT</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>35325</t>
+          <t>35912</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Lea</t>
+          <t>Tomas</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>JAMELOT</t>
+          <t>JANDA</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>35912</t>
+          <t>44435</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Tomas</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>JANDA</t>
+          <t>JANKOVEC</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -83370,17 +87040,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>44435</t>
+          <t>36728</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Mirnazim</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>JANKOVEC</t>
+          <t>JAVADOV</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -83392,17 +87062,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>36728</t>
+          <t>42351</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Mirnazim</t>
+          <t>Jeppe</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>JAVADOV</t>
+          <t>JENSBY</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -83414,17 +87084,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>42351</t>
+          <t>42488</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Jeppe</t>
+          <t>Andrew Dennis</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>JENSBY</t>
+          <t>JESSOP</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -83436,17 +87106,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>42488</t>
+          <t>42441</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Andrew Dennis</t>
+          <t>Andrzej</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>JESSOP</t>
+          <t>JEZIERSKI</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -83458,17 +87128,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>42441</t>
+          <t>35328</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Andrzej</t>
+          <t>Sebastien</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>JEZIERSKI</t>
+          <t>JOUVE</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -83480,17 +87150,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>35328</t>
+          <t>47674</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Sebastien</t>
+          <t>Ildar</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>JOUVE</t>
+          <t>KAYUMOV</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -83502,39 +87172,39 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>47674</t>
+          <t>36173</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Ildar</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>KAYUMOV</t>
+          <t>KAZAKOVA</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>36173</t>
+          <t>42559</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Inna</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>KAZAKOVA</t>
+          <t>KLINOVA</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -83546,17 +87216,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>42559</t>
+          <t>44421</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Inna</t>
+          <t>Ivana</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>KLINOVA</t>
+          <t>KMETOVA</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -83568,39 +87238,39 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>44421</t>
+          <t>47675</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Ivana</t>
+          <t>Gerasim</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>KMETOVA</t>
+          <t>KOCHNEV</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>47675</t>
+          <t>47717</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Gerasim</t>
+          <t>Rastislav</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>KOCHNEV</t>
+          <t>KOHUT</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -83612,17 +87282,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>47717</t>
+          <t>42137</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Rastislav</t>
+          <t>Artem</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>KOHUT</t>
+          <t>KONONYUK</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -83634,17 +87304,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>42137</t>
+          <t>42136</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Artem</t>
+          <t>Alexander</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>KONONYUK</t>
+          <t>KOVALENKO</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -83656,17 +87326,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>42136</t>
+          <t>42055</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Alexander</t>
+          <t>Artsem</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>KOVALENKO</t>
+          <t>KOZYR</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -83678,61 +87348,61 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>42055</t>
+          <t>35779</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Artsem</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>KOZYR</t>
+          <t>KOZISKOVA</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>35779</t>
+          <t>45732</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>KOZISKOVA</t>
+          <t>KRAJCOVIC</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>45732</t>
+          <t>35715</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>KRAJCOVIC</t>
+          <t>KRETSCHMER</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -83744,17 +87414,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>35715</t>
+          <t>35871</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Piotr</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>KRETSCHMER</t>
+          <t>KULETA</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -83766,17 +87436,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>35871</t>
+          <t>35717</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Kurt</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>KULETA</t>
+          <t>KUSCHELA</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -83788,17 +87458,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>35717</t>
+          <t>36512</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Kurt</t>
+          <t>Lukas</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>KUSCHELA</t>
+          <t>KUSOVSKY</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -83810,17 +87480,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>36512</t>
+          <t>36669</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Lukas</t>
+          <t>Fabian</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>KUSOVSKY</t>
+          <t>KUX</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -83832,17 +87502,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>36669</t>
+          <t>35915</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Fabian</t>
+          <t>Patrik</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>KUX</t>
+          <t>KUCERA</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -83854,17 +87524,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>35915</t>
+          <t>42585</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Patrik</t>
+          <t>Ka Wai</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>KUCERA</t>
+          <t>KWOK</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -83876,17 +87546,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>42585</t>
+          <t>61246</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Ka Wai</t>
+          <t>Pierre-Luc</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>KWOK</t>
+          <t>LALIBERTE</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -83898,17 +87568,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>61246</t>
+          <t>41993</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Pierre-Luc</t>
+          <t>Aurimas</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>LALIBERTE</t>
+          <t>LANKAS</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -83920,17 +87590,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>41993</t>
+          <t>42348</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Aurimas</t>
+          <t>Martin Trebbien Vestergaard</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>LANKAS</t>
+          <t>LARSEN</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -83942,17 +87612,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>42348</t>
+          <t>42257</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Martin Trebbien Vestergaard</t>
+          <t>Andres</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>LARSEN</t>
+          <t>LAZO</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -83964,17 +87634,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>42257</t>
+          <t>35380</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Andres</t>
+          <t>Vincent</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>LAZO</t>
+          <t>LECRUBIER</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -83986,61 +87656,61 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>35380</t>
+          <t>35562</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Vincent</t>
+          <t>Ana-Roxana</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>LECRUBIER</t>
+          <t>LEHACI</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>35562</t>
+          <t>35719</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Ana-Roxana</t>
+          <t>Erik</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>LEHACI</t>
+          <t>LEUE</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>35719</t>
+          <t>42063</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Erik</t>
+          <t>Aliksandr</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>LEUE</t>
+          <t>LIAPIOSHKA</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -84052,17 +87722,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>42063</t>
+          <t>35720</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Aliksandr</t>
+          <t>Tom</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>LIAPIOSHKA</t>
+          <t>LIEBSCHER-LUCZ</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -84074,39 +87744,39 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>35720</t>
+          <t>36165</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Tom</t>
+          <t>Natalia</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>LIEBSCHER-LUCZ</t>
+          <t>LOBOVA</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>36165</t>
+          <t>42461</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Natalia</t>
+          <t>Una Helen Bean</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>LOBOVA</t>
+          <t>LOUNDER</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -84118,39 +87788,39 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>42461</t>
+          <t>42353</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Una Helen Bean</t>
+          <t>Troels</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>LOUNDER</t>
+          <t>LUND</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>42353</t>
+          <t>42364</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Troels</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>LUND</t>
+          <t>LUNACEK</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -84162,17 +87832,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>42364</t>
+          <t>36185</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Kirill</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>LUNACEK</t>
+          <t>LYAPUNOV</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -84184,61 +87854,61 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>36185</t>
+          <t>46674</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Kirill</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>LYAPUNOV</t>
+          <t>MACHOVA</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>46674</t>
+          <t>42044</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Vadzim</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>MACHOVA</t>
+          <t>MAKHNEU</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>42044</t>
+          <t>42139</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Vadzim</t>
+          <t>Ruslan</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>MAKHNEU</t>
+          <t>MAMUTOV</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -84250,39 +87920,39 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>42139</t>
+          <t>36224</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Ruslan</t>
+          <t>Hayleigh-Jayne</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>MAMUTOV</t>
+          <t>MASON</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>36224</t>
+          <t>35897</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Hayleigh-Jayne</t>
+          <t>Lucie</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>MASON</t>
+          <t>MATOUSKOVA</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -84294,17 +87964,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>35897</t>
+          <t>35391</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Lucie</t>
+          <t>Joanne</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>MATOUSKOVA</t>
+          <t>MAYER</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -84316,83 +87986,83 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>35391</t>
+          <t>42487</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Joanne</t>
+          <t>Jason Stephen Reginald</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>MAYER</t>
+          <t>MCCOOMBS</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>42487</t>
+          <t>42361</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Jason Stephen Reginald</t>
+          <t>Kaitlyn</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>MCCOOMBS</t>
+          <t>MCELROY</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>42361</t>
+          <t>36226</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Kaitlyn</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>MCELROY</t>
+          <t>MCKEEVER</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>36226</t>
+          <t>36147</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>Ilya</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>MCKEEVER</t>
+          <t>MEDVEDEV</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -84404,17 +88074,17 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>36147</t>
+          <t>44426</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Ilya</t>
+          <t>Matej</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>MEDVEDEV</t>
+          <t>MICHALEK</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -84426,17 +88096,17 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>44426</t>
+          <t>35992</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Matej</t>
+          <t>Morten</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>MICHALEK</t>
+          <t>MINDE</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -84448,17 +88118,17 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>35992</t>
+          <t>42305</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Morten</t>
+          <t>Uros</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>MINDE</t>
+          <t>MITJEV</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -84470,17 +88140,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>42305</t>
+          <t>35556</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Uros</t>
+          <t>Radek</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>MITJEV</t>
+          <t>MISKOVSKY</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -84492,61 +88162,61 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>35556</t>
+          <t>42187</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Radek</t>
+          <t>Nikolina</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>MISKOVSKY</t>
+          <t>MOLDOVAN</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>42187</t>
+          <t>42389</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Nikolina</t>
+          <t>Ruslan</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>MOLDOVAN</t>
+          <t>MOLTAEV</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>42389</t>
+          <t>42464</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Ruslan</t>
+          <t>Etienne</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>MOLTAEV</t>
+          <t>MORNEAU</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -84558,17 +88228,17 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>42464</t>
+          <t>42283</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Etienne</t>
+          <t>Mohamed Ali</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>MORNEAU</t>
+          <t>MRABET</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -84580,61 +88250,61 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>42283</t>
+          <t>36562</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Mohamed Ali</t>
+          <t>Norma</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>MRABET</t>
+          <t>MURABITO</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>36562</t>
+          <t>36731</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Norma</t>
+          <t>Tamerlan</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>MURABITO</t>
+          <t>MUSTAFAYEV</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>36731</t>
+          <t>36798</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Tamerlan</t>
+          <t>Ignas</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>MUSTAFAYEV</t>
+          <t>NAVAKAUSKAS</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -84646,17 +88316,17 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>36798</t>
+          <t>36796</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Ignas</t>
+          <t>Ricardas</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>NAVAKAUSKAS</t>
+          <t>NEKRIOSIUS</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -84668,17 +88338,17 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>36796</t>
+          <t>42375</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Ricardas</t>
+          <t>Lukas</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>NEKRIOSIUS</t>
+          <t>NEPRAS</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -84690,61 +88360,61 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>42375</t>
+          <t>42427</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Lukas</t>
+          <t>Federica</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>NEPRAS</t>
+          <t>NOLE</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>42427</t>
+          <t>35723</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Federica</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>NOLE</t>
+          <t>NUCK</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>35723</t>
+          <t>42369</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>NUCK</t>
+          <t>ODVARKO</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -84756,17 +88426,17 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>42369</t>
+          <t>42466</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Mark William</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>ODVARKO</t>
+          <t>OLDERSHAW</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -84778,17 +88448,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>42466</t>
+          <t>36797</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Mark William</t>
+          <t>Andrej</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>OLDERSHAW</t>
+          <t>OLIJNIK</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -84800,17 +88470,17 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>36797</t>
+          <t>42178</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Andrej</t>
+          <t>Dejan</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>OLIJNIK</t>
+          <t>PAJIC</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -84822,105 +88492,105 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>42178</t>
+          <t>36186</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Dejan</t>
+          <t>Anastasia</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>PAJIC</t>
+          <t>PANCHENKO</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>36186</t>
+          <t>41784</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Anastasia</t>
+          <t>Laurens</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>PANCHENKO</t>
+          <t>PANNECOUCKE</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>41784</t>
+          <t>42059</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Laurens</t>
+          <t>Nadzeya</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>PANNECOUCKE</t>
+          <t>PAPOK</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>42059</t>
+          <t>42462</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Nadzeya</t>
+          <t>Aleksandr</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>PAPOK</t>
+          <t>PAROL</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>42462</t>
+          <t>41787</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Aleksandr</t>
+          <t>William</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>PAROL</t>
+          <t>PETERS</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -84932,44 +88602,44 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>41787</t>
+          <t>42426</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Cristina</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>PETERS</t>
+          <t>PETRACCA</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>42426</t>
+          <t>36163</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Cristina</t>
+          <t>Pavel</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>PETRACCA</t>
+          <t>PETROV</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>

--- a/events/Racice_2013_WC/Racice_2013_WC_Results.xlsx
+++ b/events/Racice_2013_WC/Racice_2013_WC_Results.xlsx
@@ -11596,6 +11596,11 @@
           <t>4:16.191</t>
         </is>
       </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>47779</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -44988,6 +44993,11 @@
           <t>4:04.496</t>
         </is>
       </c>
+      <c r="R681" t="inlineStr">
+        <is>
+          <t>47779</t>
+        </is>
+      </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
@@ -82250,6 +82260,11 @@
       <c r="P1252" t="inlineStr">
         <is>
           <t>23:15.0</t>
+        </is>
+      </c>
+      <c r="R1252" t="inlineStr">
+        <is>
+          <t>47779</t>
         </is>
       </c>
     </row>
@@ -84570,7 +84585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D285"/>
+  <dimension ref="A1:D286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -90843,6 +90858,28 @@
         </is>
       </c>
     </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>47779</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Krisztina</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>BEDOCS</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Racice_2013_WC/Racice_2013_WC_Results.xlsx
+++ b/events/Racice_2013_WC/Racice_2013_WC_Results.xlsx
@@ -1932,6 +1932,11 @@
           <t>2:05.220</t>
         </is>
       </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>126240</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2572,6 +2577,11 @@
           <t>2:00.241</t>
         </is>
       </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2822,6 +2832,11 @@
           <t>1:50.221</t>
         </is>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>42148</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3552,6 +3567,11 @@
           <t>2:00.791</t>
         </is>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>104031</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4142,6 +4162,11 @@
           <t>3:41.871</t>
         </is>
       </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5862,6 +5887,11 @@
           <t>3:49.181</t>
         </is>
       </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5987,6 +6017,11 @@
           <t>3:52.531</t>
         </is>
       </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6487,6 +6522,11 @@
           <t>4:16.941</t>
         </is>
       </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>36159</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -7122,6 +7162,11 @@
           <t>4:17.861</t>
         </is>
       </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>172028</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -7627,6 +7672,11 @@
           <t>3:24.941</t>
         </is>
       </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>42145</t>
+        </is>
+      </c>
       <c r="S112" t="inlineStr">
         <is>
           <t>36153</t>
@@ -8487,6 +8537,11 @@
           <t>3:49.561</t>
         </is>
       </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>71239</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -8677,6 +8732,11 @@
           <t>3:24.371</t>
         </is>
       </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>42285</t>
+        </is>
+      </c>
       <c r="S128" t="inlineStr">
         <is>
           <t>42468</t>
@@ -9227,6 +9287,11 @@
           <t>3:24.631</t>
         </is>
       </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>45529</t>
+        </is>
+      </c>
       <c r="S136" t="inlineStr">
         <is>
           <t>42488</t>
@@ -9292,6 +9357,11 @@
           <t>3:25.201</t>
         </is>
       </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>42356</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -9492,6 +9562,11 @@
           <t>41774</t>
         </is>
       </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -9742,6 +9817,16 @@
           <t>3:51.601</t>
         </is>
       </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>46671</t>
+        </is>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -9802,6 +9887,11 @@
           <t>3:56.721</t>
         </is>
       </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>42413</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -9862,6 +9952,11 @@
           <t>3:57.161</t>
         </is>
       </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>105917</t>
+        </is>
+      </c>
       <c r="S146" t="inlineStr">
         <is>
           <t>36005</t>
@@ -12516,6 +12611,11 @@
           <t>4:14.281</t>
         </is>
       </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>104031</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -13020,6 +13120,16 @@
           <t>3:16.031</t>
         </is>
       </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>42144</t>
+        </is>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>42145</t>
+        </is>
+      </c>
       <c r="U194" t="inlineStr">
         <is>
           <t>36153</t>
@@ -13090,6 +13200,11 @@
           <t>52232</t>
         </is>
       </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
       <c r="U195" t="inlineStr">
         <is>
           <t>56336</t>
@@ -13235,6 +13350,11 @@
           <t>36448</t>
         </is>
       </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>36453</t>
+        </is>
+      </c>
       <c r="T197" t="inlineStr">
         <is>
           <t>36449</t>
@@ -13980,6 +14100,11 @@
           <t>3:18.461</t>
         </is>
       </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>42169</t>
+        </is>
+      </c>
       <c r="U207" t="inlineStr">
         <is>
           <t>42165</t>
@@ -14495,6 +14620,11 @@
           <t>1:58.600</t>
         </is>
       </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -15830,6 +15960,11 @@
           <t>2:12.471</t>
         </is>
       </c>
+      <c r="R236" t="inlineStr">
+        <is>
+          <t>126240</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -16095,6 +16230,11 @@
           <t>1:53.363</t>
         </is>
       </c>
+      <c r="S240" t="inlineStr">
+        <is>
+          <t>42148</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -17020,6 +17160,11 @@
           <t>2:02.722</t>
         </is>
       </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>104031</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -17145,6 +17290,11 @@
           <t>3:39.312</t>
         </is>
       </c>
+      <c r="R256" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -17395,6 +17545,11 @@
           <t>3:42.072</t>
         </is>
       </c>
+      <c r="R260" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -17710,6 +17865,11 @@
           <t>3:44.760</t>
         </is>
       </c>
+      <c r="R265" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -18990,6 +19150,11 @@
           <t>4:08.276</t>
         </is>
       </c>
+      <c r="R285" t="inlineStr">
+        <is>
+          <t>36159</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -19310,6 +19475,11 @@
           <t>4:25.751</t>
         </is>
       </c>
+      <c r="R290" t="inlineStr">
+        <is>
+          <t>172028</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -20005,6 +20175,11 @@
           <t>3:26.440</t>
         </is>
       </c>
+      <c r="R301" t="inlineStr">
+        <is>
+          <t>42145</t>
+        </is>
+      </c>
       <c r="S301" t="inlineStr">
         <is>
           <t>36153</t>
@@ -20135,6 +20310,11 @@
           <t>3:27.706</t>
         </is>
       </c>
+      <c r="R303" t="inlineStr">
+        <is>
+          <t>42356</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -20390,6 +20570,11 @@
           <t>3:52.577</t>
         </is>
       </c>
+      <c r="R307" t="inlineStr">
+        <is>
+          <t>71239</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -20800,6 +20985,11 @@
           <t>3:29.066</t>
         </is>
       </c>
+      <c r="R313" t="inlineStr">
+        <is>
+          <t>45529</t>
+        </is>
+      </c>
       <c r="S313" t="inlineStr">
         <is>
           <t>42488</t>
@@ -20870,6 +21060,11 @@
           <t>41774</t>
         </is>
       </c>
+      <c r="S314" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -21190,6 +21385,11 @@
           <t>3:24.587</t>
         </is>
       </c>
+      <c r="R319" t="inlineStr">
+        <is>
+          <t>42285</t>
+        </is>
+      </c>
       <c r="S319" t="inlineStr">
         <is>
           <t>42468</t>
@@ -21805,6 +22005,16 @@
           <t>3:53.447</t>
         </is>
       </c>
+      <c r="R328" t="inlineStr">
+        <is>
+          <t>46671</t>
+        </is>
+      </c>
+      <c r="S328" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -21865,6 +22075,11 @@
           <t>3:53.984</t>
         </is>
       </c>
+      <c r="R329" t="inlineStr">
+        <is>
+          <t>105917</t>
+        </is>
+      </c>
       <c r="S329" t="inlineStr">
         <is>
           <t>36005</t>
@@ -21990,6 +22205,11 @@
           <t>4:07.259</t>
         </is>
       </c>
+      <c r="S331" t="inlineStr">
+        <is>
+          <t>42413</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -23380,6 +23600,11 @@
           <t>4:07.509</t>
         </is>
       </c>
+      <c r="S353" t="inlineStr">
+        <is>
+          <t>104031</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -23580,6 +23805,16 @@
           <t>2:59.006</t>
         </is>
       </c>
+      <c r="R356" t="inlineStr">
+        <is>
+          <t>42144</t>
+        </is>
+      </c>
+      <c r="S356" t="inlineStr">
+        <is>
+          <t>42145</t>
+        </is>
+      </c>
       <c r="U356" t="inlineStr">
         <is>
           <t>36153</t>
@@ -24230,6 +24465,11 @@
           <t>36448</t>
         </is>
       </c>
+      <c r="S365" t="inlineStr">
+        <is>
+          <t>36453</t>
+        </is>
+      </c>
       <c r="T365" t="inlineStr">
         <is>
           <t>36449</t>
@@ -24540,6 +24780,11 @@
           <t>52232</t>
         </is>
       </c>
+      <c r="T369" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
       <c r="U369" t="inlineStr">
         <is>
           <t>56336</t>
@@ -24605,6 +24850,11 @@
           <t>3:10.325</t>
         </is>
       </c>
+      <c r="S370" t="inlineStr">
+        <is>
+          <t>42169</t>
+        </is>
+      </c>
       <c r="U370" t="inlineStr">
         <is>
           <t>42165</t>
@@ -25879,6 +26129,11 @@
           <t>1:53.079</t>
         </is>
       </c>
+      <c r="R390" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -25939,6 +26194,11 @@
           <t>1:53.939</t>
         </is>
       </c>
+      <c r="R391" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -26558,6 +26818,11 @@
       <c r="L401" t="n">
         <v>3</v>
       </c>
+      <c r="R401" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
       <c r="X401" t="inlineStr">
         <is>
           <t>DSQ</t>
@@ -27013,6 +27278,11 @@
           <t>1:56.692</t>
         </is>
       </c>
+      <c r="R408" t="inlineStr">
+        <is>
+          <t>36159</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -27263,6 +27533,11 @@
           <t>2:08.758</t>
         </is>
       </c>
+      <c r="R412" t="inlineStr">
+        <is>
+          <t>42510</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -27513,6 +27788,11 @@
           <t>1:59.262</t>
         </is>
       </c>
+      <c r="R416" t="inlineStr">
+        <is>
+          <t>172028</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -28468,6 +28748,11 @@
           <t>1:40.620</t>
         </is>
       </c>
+      <c r="R431" t="inlineStr">
+        <is>
+          <t>41592</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -28863,6 +29148,11 @@
           <t>36450</t>
         </is>
       </c>
+      <c r="S437" t="inlineStr">
+        <is>
+          <t>36453</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -29468,6 +29758,11 @@
           <t>1:37.267</t>
         </is>
       </c>
+      <c r="R446" t="inlineStr">
+        <is>
+          <t>42285</t>
+        </is>
+      </c>
       <c r="S446" t="inlineStr">
         <is>
           <t>42468</t>
@@ -29863,6 +30158,11 @@
           <t>1:37.881</t>
         </is>
       </c>
+      <c r="R452" t="inlineStr">
+        <is>
+          <t>45529</t>
+        </is>
+      </c>
       <c r="S452" t="inlineStr">
         <is>
           <t>42488</t>
@@ -30338,6 +30638,11 @@
           <t>42151</t>
         </is>
       </c>
+      <c r="S459" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -30398,6 +30703,11 @@
           <t>1:47.770</t>
         </is>
       </c>
+      <c r="R460" t="inlineStr">
+        <is>
+          <t>42411</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -30518,6 +30828,16 @@
           <t>1:47.873</t>
         </is>
       </c>
+      <c r="R462" t="inlineStr">
+        <is>
+          <t>46671</t>
+        </is>
+      </c>
+      <c r="S462" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -30578,6 +30898,11 @@
           <t>1:48.326</t>
         </is>
       </c>
+      <c r="R463" t="inlineStr">
+        <is>
+          <t>105917</t>
+        </is>
+      </c>
       <c r="S463" t="inlineStr">
         <is>
           <t>36005</t>
@@ -32508,6 +32833,11 @@
           <t>1:48.133</t>
         </is>
       </c>
+      <c r="R493" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -32758,6 +33088,11 @@
           <t>1:40.924</t>
         </is>
       </c>
+      <c r="R497" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -34033,6 +34368,11 @@
           <t>1:56.539</t>
         </is>
       </c>
+      <c r="R517" t="inlineStr">
+        <is>
+          <t>172028</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -34283,6 +34623,11 @@
           <t>2:04.761</t>
         </is>
       </c>
+      <c r="R521" t="inlineStr">
+        <is>
+          <t>42510</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -34803,6 +35148,11 @@
           <t>1:36.881</t>
         </is>
       </c>
+      <c r="R529" t="inlineStr">
+        <is>
+          <t>42285</t>
+        </is>
+      </c>
       <c r="S529" t="inlineStr">
         <is>
           <t>42468</t>
@@ -35872,6 +36222,11 @@
           <t>1:38.787</t>
         </is>
       </c>
+      <c r="R545" t="inlineStr">
+        <is>
+          <t>45529</t>
+        </is>
+      </c>
       <c r="S545" t="inlineStr">
         <is>
           <t>42488</t>
@@ -35937,6 +36292,11 @@
           <t>1:41.960</t>
         </is>
       </c>
+      <c r="R546" t="inlineStr">
+        <is>
+          <t>41592</t>
+        </is>
+      </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
@@ -36522,6 +36882,16 @@
           <t>1:50.283</t>
         </is>
       </c>
+      <c r="R555" t="inlineStr">
+        <is>
+          <t>46671</t>
+        </is>
+      </c>
+      <c r="S555" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
@@ -36582,6 +36952,11 @@
           <t>2:01.542</t>
         </is>
       </c>
+      <c r="R556" t="inlineStr">
+        <is>
+          <t>105917</t>
+        </is>
+      </c>
       <c r="S556" t="inlineStr">
         <is>
           <t>36005</t>
@@ -36836,6 +37211,11 @@
           <t>1:52.069</t>
         </is>
       </c>
+      <c r="R560" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
@@ -37419,6 +37799,11 @@
           <t>1:46.067</t>
         </is>
       </c>
+      <c r="S569" t="inlineStr">
+        <is>
+          <t>42148</t>
+        </is>
+      </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
@@ -37970,6 +38355,11 @@
           <t>3:31.233</t>
         </is>
       </c>
+      <c r="R577" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
@@ -38568,6 +38958,11 @@
           <t>3:57.167</t>
         </is>
       </c>
+      <c r="R586" t="inlineStr">
+        <is>
+          <t>36159</t>
+        </is>
+      </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
@@ -39223,6 +39618,11 @@
           <t>3:20.434</t>
         </is>
       </c>
+      <c r="R596" t="inlineStr">
+        <is>
+          <t>42356</t>
+        </is>
+      </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
@@ -39285,6 +39685,11 @@
           <t>3:21.044</t>
         </is>
       </c>
+      <c r="R597" t="inlineStr">
+        <is>
+          <t>45529</t>
+        </is>
+      </c>
       <c r="S597" t="inlineStr">
         <is>
           <t>42488</t>
@@ -39501,6 +39906,11 @@
           <t>41774</t>
         </is>
       </c>
+      <c r="S600" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
@@ -40598,6 +41008,11 @@
           <t>52232</t>
         </is>
       </c>
+      <c r="T616" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
       <c r="U616" t="inlineStr">
         <is>
           <t>56336</t>
@@ -40963,6 +41378,11 @@
           <t>3:07.585</t>
         </is>
       </c>
+      <c r="S621" t="inlineStr">
+        <is>
+          <t>42169</t>
+        </is>
+      </c>
       <c r="U621" t="inlineStr">
         <is>
           <t>42165</t>
@@ -42303,6 +42723,11 @@
           <t>3:27.063</t>
         </is>
       </c>
+      <c r="R641" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
@@ -42365,6 +42790,11 @@
           <t>3:27.560</t>
         </is>
       </c>
+      <c r="R642" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
@@ -43916,6 +44346,11 @@
           <t>3:16.548</t>
         </is>
       </c>
+      <c r="R665" t="inlineStr">
+        <is>
+          <t>42145</t>
+        </is>
+      </c>
       <c r="S665" t="inlineStr">
         <is>
           <t>36153</t>
@@ -44549,6 +44984,16 @@
           <t>3:42.915</t>
         </is>
       </c>
+      <c r="R674" t="inlineStr">
+        <is>
+          <t>46671</t>
+        </is>
+      </c>
+      <c r="S674" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
@@ -45600,6 +46045,11 @@
           <t>3:49.671</t>
         </is>
       </c>
+      <c r="S690" t="inlineStr">
+        <is>
+          <t>104031</t>
+        </is>
+      </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
@@ -45945,6 +46395,11 @@
           <t>36448</t>
         </is>
       </c>
+      <c r="S695" t="inlineStr">
+        <is>
+          <t>36453</t>
+        </is>
+      </c>
       <c r="T695" t="inlineStr">
         <is>
           <t>36449</t>
@@ -46489,6 +46944,16 @@
           <t>2:58.183</t>
         </is>
       </c>
+      <c r="R702" t="inlineStr">
+        <is>
+          <t>42144</t>
+        </is>
+      </c>
+      <c r="S702" t="inlineStr">
+        <is>
+          <t>42145</t>
+        </is>
+      </c>
       <c r="U702" t="inlineStr">
         <is>
           <t>36153</t>
@@ -46859,6 +47324,16 @@
           <t>3:36.802</t>
         </is>
       </c>
+      <c r="R707" t="inlineStr">
+        <is>
+          <t>46671</t>
+        </is>
+      </c>
+      <c r="S707" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
       <c r="U707" t="inlineStr">
         <is>
           <t>35556</t>
@@ -46994,6 +47469,16 @@
           <t>1:34.644</t>
         </is>
       </c>
+      <c r="T709" t="inlineStr">
+        <is>
+          <t>36171</t>
+        </is>
+      </c>
+      <c r="U709" t="inlineStr">
+        <is>
+          <t>42148</t>
+        </is>
+      </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
@@ -47279,6 +47764,11 @@
           <t>42059</t>
         </is>
       </c>
+      <c r="T713" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
@@ -47569,6 +48059,11 @@
           <t>35788</t>
         </is>
       </c>
+      <c r="T717" t="inlineStr">
+        <is>
+          <t>126240</t>
+        </is>
+      </c>
       <c r="U717" t="inlineStr">
         <is>
           <t>35779</t>
@@ -48004,6 +48499,11 @@
           <t>0:37.477</t>
         </is>
       </c>
+      <c r="R724" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
@@ -48444,6 +48944,11 @@
           <t>0:36.084</t>
         </is>
       </c>
+      <c r="R731" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
@@ -48894,6 +49399,11 @@
           <t>0:35.647</t>
         </is>
       </c>
+      <c r="R738" t="inlineStr">
+        <is>
+          <t>119054</t>
+        </is>
+      </c>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
@@ -49654,6 +50164,11 @@
           <t>0:37.077</t>
         </is>
       </c>
+      <c r="R750" t="inlineStr">
+        <is>
+          <t>94131</t>
+        </is>
+      </c>
     </row>
     <row r="751">
       <c r="A751" t="inlineStr">
@@ -49779,6 +50294,11 @@
           <t>0:49.319</t>
         </is>
       </c>
+      <c r="R752" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="753">
       <c r="A753" t="inlineStr">
@@ -50854,6 +51374,11 @@
           <t>0:39.707</t>
         </is>
       </c>
+      <c r="R769" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
     </row>
     <row r="770">
       <c r="A770" t="inlineStr">
@@ -51289,6 +51814,11 @@
           <t>0:39.973</t>
         </is>
       </c>
+      <c r="R776" t="inlineStr">
+        <is>
+          <t>42411</t>
+        </is>
+      </c>
     </row>
     <row r="777">
       <c r="A777" t="inlineStr">
@@ -51859,6 +52389,11 @@
           <t>0:40.826</t>
         </is>
       </c>
+      <c r="R785" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
     </row>
     <row r="786">
       <c r="A786" t="inlineStr">
@@ -52869,6 +53404,11 @@
           <t>0:41.086</t>
         </is>
       </c>
+      <c r="R801" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
     </row>
     <row r="802">
       <c r="A802" t="inlineStr">
@@ -54473,6 +55013,11 @@
           <t>0:33.031</t>
         </is>
       </c>
+      <c r="R826" t="inlineStr">
+        <is>
+          <t>42511</t>
+        </is>
+      </c>
     </row>
     <row r="827">
       <c r="A827" t="inlineStr">
@@ -55992,6 +56537,11 @@
           <t>0:33.007</t>
         </is>
       </c>
+      <c r="R849" t="inlineStr">
+        <is>
+          <t>147929</t>
+        </is>
+      </c>
     </row>
     <row r="850">
       <c r="A850" t="inlineStr">
@@ -56327,6 +56877,11 @@
           <t>0:38.293</t>
         </is>
       </c>
+      <c r="S854" t="inlineStr">
+        <is>
+          <t>42413</t>
+        </is>
+      </c>
     </row>
     <row r="855">
       <c r="A855" t="inlineStr">
@@ -56517,6 +57072,11 @@
           <t>0:39.350</t>
         </is>
       </c>
+      <c r="R857" t="inlineStr">
+        <is>
+          <t>105917</t>
+        </is>
+      </c>
       <c r="S857" t="inlineStr">
         <is>
           <t>36005</t>
@@ -58152,6 +58712,11 @@
           <t>0:51.515</t>
         </is>
       </c>
+      <c r="R882" t="inlineStr">
+        <is>
+          <t>75474</t>
+        </is>
+      </c>
     </row>
     <row r="883">
       <c r="A883" t="inlineStr">
@@ -58852,6 +59417,11 @@
           <t>35788</t>
         </is>
       </c>
+      <c r="T893" t="inlineStr">
+        <is>
+          <t>126240</t>
+        </is>
+      </c>
       <c r="U893" t="inlineStr">
         <is>
           <t>35779</t>
@@ -59952,6 +60522,11 @@
           <t>0:36.340</t>
         </is>
       </c>
+      <c r="R910" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
     </row>
     <row r="911">
       <c r="A911" t="inlineStr">
@@ -60522,6 +61097,11 @@
           <t>0:36.524</t>
         </is>
       </c>
+      <c r="R919" t="inlineStr">
+        <is>
+          <t>119054</t>
+        </is>
+      </c>
     </row>
     <row r="920">
       <c r="A920" t="inlineStr">
@@ -60582,6 +61162,11 @@
           <t>0:36.527</t>
         </is>
       </c>
+      <c r="R920" t="inlineStr">
+        <is>
+          <t>94131</t>
+        </is>
+      </c>
     </row>
     <row r="921">
       <c r="A921" t="inlineStr">
@@ -60707,6 +61292,11 @@
           <t>0:36.634</t>
         </is>
       </c>
+      <c r="R922" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
     </row>
     <row r="923">
       <c r="A923" t="inlineStr">
@@ -61326,6 +61916,11 @@
           <t>0:39.547</t>
         </is>
       </c>
+      <c r="R932" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
     </row>
     <row r="933">
       <c r="A933" t="inlineStr">
@@ -61581,6 +62176,11 @@
           <t>0:40.776</t>
         </is>
       </c>
+      <c r="R936" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
     </row>
     <row r="937">
       <c r="A937" t="inlineStr">
@@ -62516,6 +63116,11 @@
           <t>0:39.643</t>
         </is>
       </c>
+      <c r="R951" t="inlineStr">
+        <is>
+          <t>42411</t>
+        </is>
+      </c>
     </row>
     <row r="952">
       <c r="A952" t="inlineStr">
@@ -63026,6 +63631,11 @@
           <t>0:39.687</t>
         </is>
       </c>
+      <c r="R959" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
     </row>
     <row r="960">
       <c r="A960" t="inlineStr">
@@ -65021,6 +65631,11 @@
           <t>0:33.134</t>
         </is>
       </c>
+      <c r="R990" t="inlineStr">
+        <is>
+          <t>147929</t>
+        </is>
+      </c>
     </row>
     <row r="991">
       <c r="A991" t="inlineStr">
@@ -65611,6 +66226,11 @@
           <t>0:32.467</t>
         </is>
       </c>
+      <c r="R999" t="inlineStr">
+        <is>
+          <t>42511</t>
+        </is>
+      </c>
     </row>
     <row r="1000">
       <c r="A1000" t="inlineStr">
@@ -66745,6 +67365,11 @@
           <t>0:39.157</t>
         </is>
       </c>
+      <c r="R1016" t="inlineStr">
+        <is>
+          <t>105917</t>
+        </is>
+      </c>
       <c r="S1016" t="inlineStr">
         <is>
           <t>36005</t>
@@ -67705,6 +68330,11 @@
           <t>0:52.402</t>
         </is>
       </c>
+      <c r="R1031" t="inlineStr">
+        <is>
+          <t>75474</t>
+        </is>
+      </c>
     </row>
     <row r="1032">
       <c r="A1032" t="inlineStr">
@@ -68284,6 +68914,11 @@
           <t>1:50.209</t>
         </is>
       </c>
+      <c r="R1040" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
     </row>
     <row r="1041">
       <c r="A1041" t="inlineStr">
@@ -69186,6 +69821,11 @@
           <t>1:57.689</t>
         </is>
       </c>
+      <c r="R1054" t="inlineStr">
+        <is>
+          <t>42510</t>
+        </is>
+      </c>
     </row>
     <row r="1055">
       <c r="A1055" t="inlineStr">
@@ -69707,6 +70347,11 @@
           <t>0:37.237</t>
         </is>
       </c>
+      <c r="R1062" t="inlineStr">
+        <is>
+          <t>119054</t>
+        </is>
+      </c>
     </row>
     <row r="1063">
       <c r="A1063" t="inlineStr">
@@ -69965,6 +70610,11 @@
           <t>0:37.497</t>
         </is>
       </c>
+      <c r="R1066" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
     </row>
     <row r="1067">
       <c r="A1067" t="inlineStr">
@@ -71136,6 +71786,11 @@
           <t>0:43.336</t>
         </is>
       </c>
+      <c r="R1084" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
     </row>
     <row r="1085">
       <c r="A1085" t="inlineStr">
@@ -71920,6 +72575,11 @@
           <t>0:34.030</t>
         </is>
       </c>
+      <c r="R1096" t="inlineStr">
+        <is>
+          <t>42511</t>
+        </is>
+      </c>
     </row>
     <row r="1097">
       <c r="A1097" t="inlineStr">
@@ -72265,6 +72925,11 @@
           <t>0:35.297</t>
         </is>
       </c>
+      <c r="R1101" t="inlineStr">
+        <is>
+          <t>147929</t>
+        </is>
+      </c>
     </row>
     <row r="1102">
       <c r="A1102" t="inlineStr">
@@ -72538,6 +73203,11 @@
           <t>42059</t>
         </is>
       </c>
+      <c r="T1105" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
     </row>
     <row r="1106">
       <c r="A1106" t="inlineStr">
@@ -72836,6 +73506,11 @@
           <t>35788</t>
         </is>
       </c>
+      <c r="T1109" t="inlineStr">
+        <is>
+          <t>126240</t>
+        </is>
+      </c>
       <c r="U1109" t="inlineStr">
         <is>
           <t>35779</t>
@@ -73052,6 +73727,16 @@
           <t>1:44.597</t>
         </is>
       </c>
+      <c r="T1112" t="inlineStr">
+        <is>
+          <t>36171</t>
+        </is>
+      </c>
+      <c r="U1112" t="inlineStr">
+        <is>
+          <t>42148</t>
+        </is>
+      </c>
     </row>
     <row r="1113">
       <c r="A1113" t="inlineStr">
@@ -73196,6 +73881,11 @@
           <t>1:44.007</t>
         </is>
       </c>
+      <c r="R1114" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="1115">
       <c r="A1115" t="inlineStr">
@@ -73995,6 +74685,11 @@
           <t>1:59.109</t>
         </is>
       </c>
+      <c r="R1126" t="inlineStr">
+        <is>
+          <t>36159</t>
+        </is>
+      </c>
     </row>
     <row r="1127">
       <c r="A1127" t="inlineStr">
@@ -74258,6 +74953,11 @@
           <t>2:01.862</t>
         </is>
       </c>
+      <c r="R1130" t="inlineStr">
+        <is>
+          <t>172028</t>
+        </is>
+      </c>
     </row>
     <row r="1131">
       <c r="A1131" t="inlineStr">
@@ -74980,6 +75680,11 @@
           <t>0:40.663</t>
         </is>
       </c>
+      <c r="R1141" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
     </row>
     <row r="1142">
       <c r="A1142" t="inlineStr">
@@ -75238,6 +75943,11 @@
           <t>0:42.180</t>
         </is>
       </c>
+      <c r="R1145" t="inlineStr">
+        <is>
+          <t>42411</t>
+        </is>
+      </c>
     </row>
     <row r="1146">
       <c r="A1146" t="inlineStr">
@@ -75630,6 +76340,11 @@
           <t>0:41.963</t>
         </is>
       </c>
+      <c r="R1151" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
     </row>
     <row r="1152">
       <c r="A1152" t="inlineStr">
@@ -77216,6 +77931,11 @@
           <t>0:40.463</t>
         </is>
       </c>
+      <c r="S1174" t="inlineStr">
+        <is>
+          <t>42413</t>
+        </is>
+      </c>
     </row>
     <row r="1175">
       <c r="A1175" t="inlineStr">
@@ -78613,6 +79333,11 @@
           <t>42468</t>
         </is>
       </c>
+      <c r="S1195" t="inlineStr">
+        <is>
+          <t>42285</t>
+        </is>
+      </c>
     </row>
     <row r="1196">
       <c r="A1196" t="inlineStr">
@@ -78742,6 +79467,11 @@
           <t>1:37.627</t>
         </is>
       </c>
+      <c r="R1197" t="inlineStr">
+        <is>
+          <t>45529</t>
+        </is>
+      </c>
       <c r="S1197" t="inlineStr">
         <is>
           <t>42488</t>
@@ -79092,6 +79822,11 @@
           <t>1:42.550</t>
         </is>
       </c>
+      <c r="R1202" t="inlineStr">
+        <is>
+          <t>41592</t>
+        </is>
+      </c>
     </row>
     <row r="1203">
       <c r="A1203" t="inlineStr">
@@ -80013,6 +80748,11 @@
           <t>42151</t>
         </is>
       </c>
+      <c r="S1215" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
     </row>
     <row r="1216">
       <c r="A1216" t="inlineStr">
@@ -80147,6 +80887,11 @@
           <t>1:49.583</t>
         </is>
       </c>
+      <c r="R1217" t="inlineStr">
+        <is>
+          <t>42411</t>
+        </is>
+      </c>
     </row>
     <row r="1218">
       <c r="A1218" t="inlineStr">
@@ -80878,6 +81623,11 @@
       <c r="L1228" t="n">
         <v>5</v>
       </c>
+      <c r="R1228" t="inlineStr">
+        <is>
+          <t>75474</t>
+        </is>
+      </c>
       <c r="S1228" t="inlineStr">
         <is>
           <t>42258</t>
@@ -82772,6 +83522,11 @@
           <t>19:49.0</t>
         </is>
       </c>
+      <c r="R1261" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="1262">
       <c r="A1262" t="inlineStr">
@@ -82826,6 +83581,11 @@
           <t>19:50.6</t>
         </is>
       </c>
+      <c r="R1262" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="1263">
       <c r="A1263" t="inlineStr">
@@ -84260,6 +85020,11 @@
           <t>155</t>
         </is>
       </c>
+      <c r="R1287" t="inlineStr">
+        <is>
+          <t>36205</t>
+        </is>
+      </c>
       <c r="X1287" t="inlineStr">
         <is>
           <t>DNS</t>
@@ -84518,6 +85283,11 @@
       <c r="K1292" t="inlineStr">
         <is>
           <t>155</t>
+        </is>
+      </c>
+      <c r="R1292" t="inlineStr">
+        <is>
+          <t>52228</t>
         </is>
       </c>
       <c r="X1292" t="inlineStr">
@@ -84585,7 +85355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D286"/>
+  <dimension ref="A1:D318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -90880,6 +91650,710 @@
         </is>
       </c>
     </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Dan</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>DRAHOKOUPIL</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Ivan</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>SHTYL</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>36159</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Ilia</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>SHTOKALOV</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Natalia</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>PODOLSKAIA</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>36171</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Elena</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>ANIUSHINA</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>36453</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Joao</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>RIBEIRO</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Miika</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>NYKAENEN</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Aleh</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>YURENIA</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Volha</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>KHUDZENKA</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>42144</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Aleksandr</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>SERGEEV</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>42145</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Maxim</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>SPESIVTSEV</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>42148</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Svetlana</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>CHERNIGOVSKAYA</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Kenny</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>WALLACE</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>42169</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>BANNISTER</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>42356</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Nils Jensen</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>BOE</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Timothy</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>HORNSBY</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>42411</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Helder</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>SILVA</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>42413</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Nuno</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>SILVA</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>42510</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Yul</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>OELTZE</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>42511</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Martin</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>SCHUBERT</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>45529</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Robert Michael James</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>CLARKE</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>46671</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Vojtech</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>RUSO</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Aleksey</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>MOCHALOV</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>71239</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Kaibo</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>75474</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Mia</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>FRIEND CHUNG</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>94131</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>David James</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>GERBER</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>104031</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Xiaoyun</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>ZENG</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>105917</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Jakub</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>SITKOWSKI</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>119054</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Lasse Bro</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>MADSEN</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>126240</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Jana</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>BLAHOVA</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>147929</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Jiri</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>KRAFT</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>172028</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Oleg</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>SHELEGOV</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Racice_2013_WC/Racice_2013_WC_Results.xlsx
+++ b/events/Racice_2013_WC/Racice_2013_WC_Results.xlsx
@@ -13970,6 +13970,11 @@
           <t>42881</t>
         </is>
       </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>42452</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -24110,6 +24115,11 @@
           <t>42881</t>
         </is>
       </c>
+      <c r="U360" t="inlineStr">
+        <is>
+          <t>42452</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -41242,6 +41252,11 @@
       <c r="R619" t="inlineStr">
         <is>
           <t>42881</t>
+        </is>
+      </c>
+      <c r="U619" t="inlineStr">
+        <is>
+          <t>42452</t>
         </is>
       </c>
     </row>
@@ -85355,7 +85370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D318"/>
+  <dimension ref="A1:D319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92354,6 +92369,28 @@
         </is>
       </c>
     </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>42452</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Phillippe</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>DUCHESNAU</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
